--- a/WorkBot/refactor-experimental/data/orders/Hillcrest Dairy/Hillcrest Dairy_Downtown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Hillcrest Dairy/Hillcrest Dairy_Downtown_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Milk - 2%</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>16.08</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>209.04</t>
-        </is>
+      <c r="C2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>209.04</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Milk - Chocolate (12/16oz)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>16.20</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>32.40</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>32.4</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Milk - Skim</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>15.56</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>15.56</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="E4" t="n">
+        <v>15.56</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Milk - Whole</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>16.08</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>16.08</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>16.08</v>
       </c>
     </row>
   </sheetData>
